--- a/token_metrics/carlos_2/delta_mode_0/eval_carlos_delta0.xlsx
+++ b/token_metrics/carlos_2/delta_mode_0/eval_carlos_delta0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Università - Borsa di Ricerca\HDT Framework Repo\HumanDigitalTwin\token_metrics\carlos_2\delta_mode_0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45EFA11-2B09-48A5-9389-6D5719C335B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6D6A850-0C1E-4AED-A937-869A6CCBF919}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Queries" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="190">
   <si>
     <t>dataset</t>
   </si>
@@ -620,6 +620,15 @@
   </si>
   <si>
     <t>Accuracy Completeness</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>Unknown</t>
   </si>
 </sst>
 </file>
@@ -666,7 +675,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -674,6 +683,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1064,12 +1075,15 @@
       <c r="I2" t="s">
         <v>20</v>
       </c>
+      <c r="J2" s="3">
+        <v>0.25</v>
+      </c>
       <c r="K2" s="2">
         <f t="shared" ref="K2:K41" si="0">IF(LOWER(TRIM(J2))=LOWER(TRIM(I2)),1,0)</f>
         <v>0</v>
       </c>
       <c r="L2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2" t="s">
         <v>21</v>
@@ -1100,12 +1114,15 @@
       <c r="I3" t="s">
         <v>26</v>
       </c>
+      <c r="J3" t="s">
+        <v>68</v>
+      </c>
       <c r="K3" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L3" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3" t="s">
         <v>27</v>
@@ -1139,9 +1156,12 @@
       <c r="I4" t="s">
         <v>34</v>
       </c>
+      <c r="J4" t="s">
+        <v>34</v>
+      </c>
       <c r="K4" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="2">
         <v>0</v>
@@ -1178,9 +1198,12 @@
       <c r="I5" t="s">
         <v>40</v>
       </c>
+      <c r="J5" t="s">
+        <v>40</v>
+      </c>
       <c r="K5" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2">
         <v>0</v>
@@ -1217,9 +1240,12 @@
       <c r="I6" t="s">
         <v>40</v>
       </c>
+      <c r="J6" t="s">
+        <v>40</v>
+      </c>
       <c r="K6" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" s="2">
         <v>0</v>
@@ -1253,12 +1279,15 @@
       <c r="I7" t="s">
         <v>51</v>
       </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
       <c r="K7" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="s">
         <v>52</v>
@@ -1289,9 +1318,12 @@
       <c r="I8" t="s">
         <v>26</v>
       </c>
+      <c r="J8" t="s">
+        <v>26</v>
+      </c>
       <c r="K8" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2">
         <v>0</v>
@@ -1325,9 +1357,12 @@
       <c r="I9" t="s">
         <v>26</v>
       </c>
+      <c r="J9" t="s">
+        <v>26</v>
+      </c>
       <c r="K9" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" s="2">
         <v>0</v>
@@ -1361,9 +1396,12 @@
       <c r="I10" t="s">
         <v>64</v>
       </c>
+      <c r="J10" t="s">
+        <v>64</v>
+      </c>
       <c r="K10" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" s="2">
         <v>0</v>
@@ -1397,9 +1435,12 @@
       <c r="I11" t="s">
         <v>68</v>
       </c>
+      <c r="J11" t="s">
+        <v>68</v>
+      </c>
       <c r="K11" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" s="2">
         <v>0</v>
@@ -1436,9 +1477,12 @@
       <c r="I12" t="s">
         <v>40</v>
       </c>
+      <c r="J12" t="s">
+        <v>40</v>
+      </c>
       <c r="K12" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12" s="2">
         <v>0</v>
@@ -1475,9 +1519,12 @@
       <c r="I13" t="s">
         <v>40</v>
       </c>
+      <c r="J13" t="s">
+        <v>40</v>
+      </c>
       <c r="K13" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="2">
         <v>0</v>
@@ -1514,9 +1561,12 @@
       <c r="I14" t="s">
         <v>40</v>
       </c>
+      <c r="J14" t="s">
+        <v>40</v>
+      </c>
       <c r="K14" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="2">
         <v>0</v>
@@ -1550,12 +1600,15 @@
       <c r="I15" t="s">
         <v>51</v>
       </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
       <c r="K15" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L15" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="s">
         <v>84</v>
@@ -1586,9 +1639,12 @@
       <c r="I16" t="s">
         <v>26</v>
       </c>
+      <c r="J16" t="s">
+        <v>26</v>
+      </c>
       <c r="K16" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" s="2">
         <v>0</v>
@@ -1622,9 +1678,12 @@
       <c r="I17" t="s">
         <v>26</v>
       </c>
+      <c r="J17" t="s">
+        <v>26</v>
+      </c>
       <c r="K17" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2">
         <v>0</v>
@@ -1658,9 +1717,12 @@
       <c r="I18" t="s">
         <v>93</v>
       </c>
+      <c r="J18" t="s">
+        <v>93</v>
+      </c>
       <c r="K18" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L18" s="2">
         <v>0</v>
@@ -1694,9 +1756,12 @@
       <c r="I19" t="s">
         <v>26</v>
       </c>
+      <c r="J19" t="s">
+        <v>26</v>
+      </c>
       <c r="K19" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2">
         <v>0</v>
@@ -1733,12 +1798,15 @@
       <c r="I20" t="s">
         <v>34</v>
       </c>
+      <c r="J20" t="s">
+        <v>187</v>
+      </c>
       <c r="K20" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L20" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N20" t="s">
         <v>101</v>
@@ -1772,9 +1840,12 @@
       <c r="I21" t="s">
         <v>34</v>
       </c>
+      <c r="J21" t="s">
+        <v>34</v>
+      </c>
       <c r="K21" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2">
         <v>0</v>
@@ -1811,9 +1882,12 @@
       <c r="I22" t="s">
         <v>40</v>
       </c>
+      <c r="J22" t="s">
+        <v>40</v>
+      </c>
       <c r="K22" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" s="2">
         <v>0</v>
@@ -1847,9 +1921,12 @@
       <c r="I23" t="s">
         <v>51</v>
       </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
       <c r="K23" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" s="2">
         <v>0</v>
@@ -1883,9 +1960,12 @@
       <c r="I24" t="s">
         <v>26</v>
       </c>
+      <c r="J24" t="s">
+        <v>26</v>
+      </c>
       <c r="K24" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2">
         <v>0</v>
@@ -1919,9 +1999,12 @@
       <c r="I25" t="s">
         <v>26</v>
       </c>
+      <c r="J25" t="s">
+        <v>26</v>
+      </c>
       <c r="K25" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L25" s="2">
         <v>0</v>
@@ -1955,12 +2038,15 @@
       <c r="I26" t="s">
         <v>120</v>
       </c>
+      <c r="J26" s="3">
+        <v>0.375</v>
+      </c>
       <c r="K26" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L26" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N26" t="s">
         <v>121</v>
@@ -1991,9 +2077,12 @@
       <c r="I27" t="s">
         <v>68</v>
       </c>
+      <c r="J27" t="s">
+        <v>68</v>
+      </c>
       <c r="K27" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" s="2">
         <v>0</v>
@@ -2030,9 +2119,12 @@
       <c r="I28" t="s">
         <v>34</v>
       </c>
+      <c r="J28" t="s">
+        <v>34</v>
+      </c>
       <c r="K28" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2">
         <v>0</v>
@@ -2069,9 +2161,12 @@
       <c r="I29" t="s">
         <v>34</v>
       </c>
+      <c r="J29" t="s">
+        <v>34</v>
+      </c>
       <c r="K29" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2">
         <v>0</v>
@@ -2108,12 +2203,15 @@
       <c r="I30" t="s">
         <v>34</v>
       </c>
+      <c r="J30" t="s">
+        <v>188</v>
+      </c>
       <c r="K30" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L30" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N30" t="s">
         <v>136</v>
@@ -2144,12 +2242,15 @@
       <c r="I31" t="s">
         <v>139</v>
       </c>
+      <c r="J31">
+        <v>6</v>
+      </c>
       <c r="K31" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L31" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N31" t="s">
         <v>140</v>
@@ -2180,9 +2281,12 @@
       <c r="I32" t="s">
         <v>26</v>
       </c>
+      <c r="J32" t="s">
+        <v>26</v>
+      </c>
       <c r="K32" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2">
         <v>0</v>
@@ -2216,9 +2320,12 @@
       <c r="I33" t="s">
         <v>26</v>
       </c>
+      <c r="J33" t="s">
+        <v>26</v>
+      </c>
       <c r="K33" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L33" s="2">
         <v>0</v>
@@ -2252,6 +2359,9 @@
       <c r="I34" t="s">
         <v>149</v>
       </c>
+      <c r="J34" t="s">
+        <v>189</v>
+      </c>
       <c r="K34" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2288,9 +2398,12 @@
       <c r="I35" t="s">
         <v>26</v>
       </c>
+      <c r="J35" t="s">
+        <v>26</v>
+      </c>
       <c r="K35" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L35" s="2">
         <v>0</v>
@@ -2327,12 +2440,15 @@
       <c r="I36" t="s">
         <v>34</v>
       </c>
+      <c r="J36" t="s">
+        <v>40</v>
+      </c>
       <c r="K36" s="2">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L36" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N36" t="s">
         <v>157</v>
@@ -2366,9 +2482,12 @@
       <c r="I37" t="s">
         <v>34</v>
       </c>
+      <c r="J37" t="s">
+        <v>34</v>
+      </c>
       <c r="K37" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L37" s="2">
         <v>0</v>
@@ -2405,9 +2524,12 @@
       <c r="I38" t="s">
         <v>34</v>
       </c>
+      <c r="J38" t="s">
+        <v>34</v>
+      </c>
       <c r="K38" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L38" s="2">
         <v>0</v>
@@ -2441,9 +2563,12 @@
       <c r="I39" t="s">
         <v>51</v>
       </c>
+      <c r="J39">
+        <v>1</v>
+      </c>
       <c r="K39" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" s="2">
         <v>0</v>
@@ -2477,9 +2602,12 @@
       <c r="I40" t="s">
         <v>26</v>
       </c>
+      <c r="J40" t="s">
+        <v>26</v>
+      </c>
       <c r="K40" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" s="2">
         <v>0</v>
@@ -2513,9 +2641,12 @@
       <c r="I41" t="s">
         <v>26</v>
       </c>
+      <c r="J41" t="s">
+        <v>26</v>
+      </c>
       <c r="K41" s="2">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2">
         <v>0</v>
@@ -2560,18 +2691,18 @@
       <c r="A3" t="s">
         <v>178</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="4">
         <f>AVERAGE(Queries!K2:K41)</f>
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>179</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="4">
         <f>IF(COUNTA(Queries!A2:A41)=0,0,SUM(Queries!L2:L41)/COUNTA(Queries!A2:A41))</f>
-        <v>0</v>
+        <v>0.22500000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.45">
@@ -2586,45 +2717,45 @@
       <c r="A6" t="s">
         <v>181</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="4">
         <f>IF(COUNTIF(Queries!E2:E41,"temporal")=0,"",AVERAGEIF(Queries!E2:E41,"temporal",Queries!K2:K41))</f>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>182</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="4">
         <f>IF(COUNTIF(Queries!E2:E41,"cross_modal")=0,"",AVERAGEIF(Queries!E2:E41,"cross_modal",Queries!K2:K41))</f>
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>183</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="4">
         <f>IF(COUNTIF(Queries!E2:E41,"deduplication")=0,"",AVERAGEIF(Queries!E2:E41,"deduplication",Queries!K2:K41))</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>184</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="4">
         <f>IF(COUNTIF(Queries!E2:E41,"hallucination")=0,"",AVERAGEIF(Queries!E2:E41,"hallucination",Queries!K2:K41))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>186</v>
       </c>
-      <c r="B10" cm="1">
+      <c r="B10" s="4" cm="1">
         <f t="array" ref="B10">IF(SUMPRODUCT(--(Queries!E2:E41&lt;&gt;"hallucination"))=0,"",1-SUMPRODUCT(--(Queries!E2:E41&lt;&gt;"hallucination"),--(((LOWER(TRIM(Queries!J2:J41))="unknown")+(TRIM(Queries!J2:J41)=""))&gt;0))/SUMPRODUCT(--(Queries!E2:E41&lt;&gt;"hallucination")))</f>
-        <v>0</v>
+        <v>0.96666666666666667</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.45">
